--- a/reportes/inventario.xlsx
+++ b/reportes/inventario.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +430,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>uniforme de gala</v>
+        <v>gala</v>
       </c>
       <c r="B2" t="str">
         <v>Uniformes</v>
@@ -445,21 +445,21 @@
         <v>L</v>
       </c>
       <c r="F2">
-        <v>50000</v>
+        <v>130000</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2" t="str">
-        <v>1000010001NaN</v>
+        <v>1000010002NaN</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>uniforme de gala</v>
+        <v>gala</v>
       </c>
       <c r="B3" t="str">
         <v>Uniformes</v>
@@ -474,21 +474,50 @@
         <v>M</v>
       </c>
       <c r="F3">
-        <v>48000</v>
+        <v>120000</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" t="str">
-        <v>1000010002NaN</v>
+        <v>1000010001NaN</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>gala</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Uniformes</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Guanenta</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Hombre</v>
+      </c>
+      <c r="E4" t="str">
+        <v>S</v>
+      </c>
+      <c r="F4">
+        <v>110000</v>
+      </c>
+      <c r="G4">
+        <v>48</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4" t="str">
+        <v>1000010003NaN</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/inventario.xlsx
+++ b/reportes/inventario.xlsx
@@ -448,7 +448,7 @@
         <v>65000</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>8</v>

--- a/reportes/inventario.xlsx
+++ b/reportes/inventario.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I286"/>
+  <dimension ref="A1:J286"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,12 +419,15 @@
         <v>Precio</v>
       </c>
       <c r="G1" t="str">
+        <v>Precio costo</v>
+      </c>
+      <c r="H1" t="str">
         <v>Cantidad</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Stock minimo</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Codigo de barras</v>
       </c>
     </row>
@@ -448,12 +451,15 @@
         <v>65000</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8</v>
-      </c>
-      <c r="I2" t="str">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2" t="str">
         <v>1000039002388</v>
       </c>
     </row>
@@ -477,12 +483,15 @@
         <v>45000</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3" t="str">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3" t="str">
         <v>1000040002391</v>
       </c>
     </row>
@@ -506,12 +515,15 @@
         <v>45000</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
-      </c>
-      <c r="I4" t="str">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4" t="str">
         <v>1000040002407</v>
       </c>
     </row>
@@ -535,12 +547,15 @@
         <v>48000</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5" t="str">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5" t="str">
         <v>1000040002414</v>
       </c>
     </row>
@@ -564,12 +579,15 @@
         <v>45000</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6" t="str">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6" t="str">
         <v>1000016000888</v>
       </c>
     </row>
@@ -593,12 +611,15 @@
         <v>45000</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7" t="str">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" t="str">
         <v>1000016000895</v>
       </c>
     </row>
@@ -622,12 +643,15 @@
         <v>48000</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
-      </c>
-      <c r="I8" t="str">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>8</v>
+      </c>
+      <c r="J8" t="str">
         <v>1000016000918</v>
       </c>
     </row>
@@ -651,12 +675,15 @@
         <v>45000</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>8</v>
-      </c>
-      <c r="I9" t="str">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9" t="str">
         <v>1000016000901</v>
       </c>
     </row>
@@ -680,12 +707,15 @@
         <v>55000</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>8</v>
-      </c>
-      <c r="I10" t="str">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10" t="str">
         <v>1000017000924</v>
       </c>
     </row>
@@ -709,12 +739,15 @@
         <v>55000</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>8</v>
-      </c>
-      <c r="I11" t="str">
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11" t="str">
         <v>1000017000931</v>
       </c>
     </row>
@@ -738,12 +771,15 @@
         <v>60000</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>8</v>
-      </c>
-      <c r="I12" t="str">
+        <v>9</v>
+      </c>
+      <c r="I12">
+        <v>8</v>
+      </c>
+      <c r="J12" t="str">
         <v>1000017000955</v>
       </c>
     </row>
@@ -767,12 +803,15 @@
         <v>55000</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>8</v>
-      </c>
-      <c r="I13" t="str">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>8</v>
+      </c>
+      <c r="J13" t="str">
         <v>1000017000948</v>
       </c>
     </row>
@@ -796,12 +835,15 @@
         <v>35000</v>
       </c>
       <c r="G14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>8</v>
-      </c>
-      <c r="I14" t="str">
+        <v>9</v>
+      </c>
+      <c r="I14">
+        <v>8</v>
+      </c>
+      <c r="J14" t="str">
         <v>1000010000495</v>
       </c>
     </row>
@@ -825,12 +867,15 @@
         <v>30000</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>8</v>
-      </c>
-      <c r="I15" t="str">
+        <v>10</v>
+      </c>
+      <c r="I15">
+        <v>8</v>
+      </c>
+      <c r="J15" t="str">
         <v>1000010000488</v>
       </c>
     </row>
@@ -854,12 +899,15 @@
         <v>46000</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>8</v>
-      </c>
-      <c r="I16" t="str">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16" t="str">
         <v>1000004000067</v>
       </c>
     </row>
@@ -883,12 +931,15 @@
         <v>50000</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>8</v>
-      </c>
-      <c r="I17" t="str">
+        <v>10</v>
+      </c>
+      <c r="I17">
+        <v>8</v>
+      </c>
+      <c r="J17" t="str">
         <v>1000018000978</v>
       </c>
     </row>
@@ -912,12 +963,15 @@
         <v>44000</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>8</v>
-      </c>
-      <c r="I18" t="str">
+        <v>10</v>
+      </c>
+      <c r="I18">
+        <v>8</v>
+      </c>
+      <c r="J18" t="str">
         <v>1000046002487</v>
       </c>
     </row>
@@ -941,12 +995,15 @@
         <v>48000</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>8</v>
-      </c>
-      <c r="I19" t="str">
+        <v>10</v>
+      </c>
+      <c r="I19">
+        <v>8</v>
+      </c>
+      <c r="J19" t="str">
         <v>1000004000074</v>
       </c>
     </row>
@@ -970,12 +1027,15 @@
         <v>52000</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>8</v>
-      </c>
-      <c r="I20" t="str">
+        <v>10</v>
+      </c>
+      <c r="I20">
+        <v>8</v>
+      </c>
+      <c r="J20" t="str">
         <v>1000018000985</v>
       </c>
     </row>
@@ -999,12 +1059,15 @@
         <v>46000</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>8</v>
-      </c>
-      <c r="I21" t="str">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>8</v>
+      </c>
+      <c r="J21" t="str">
         <v>1000046002494</v>
       </c>
     </row>
@@ -1028,12 +1091,15 @@
         <v>44000</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>8</v>
-      </c>
-      <c r="I22" t="str">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>8</v>
+      </c>
+      <c r="J22" t="str">
         <v>1000004000050</v>
       </c>
     </row>
@@ -1057,12 +1123,15 @@
         <v>48000</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>8</v>
-      </c>
-      <c r="I23" t="str">
+        <v>10</v>
+      </c>
+      <c r="I23">
+        <v>8</v>
+      </c>
+      <c r="J23" t="str">
         <v>1000018000961</v>
       </c>
     </row>
@@ -1086,12 +1155,15 @@
         <v>41000</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>8</v>
-      </c>
-      <c r="I24" t="str">
+        <v>10</v>
+      </c>
+      <c r="I24">
+        <v>8</v>
+      </c>
+      <c r="J24" t="str">
         <v>1000046002470</v>
       </c>
     </row>
@@ -1115,12 +1187,15 @@
         <v>53000</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>8</v>
-      </c>
-      <c r="I25" t="str">
+        <v>10</v>
+      </c>
+      <c r="I25">
+        <v>8</v>
+      </c>
+      <c r="J25" t="str">
         <v>1000004000098</v>
       </c>
     </row>
@@ -1144,12 +1219,15 @@
         <v>57000</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>8</v>
-      </c>
-      <c r="I26" t="str">
+        <v>10</v>
+      </c>
+      <c r="I26">
+        <v>8</v>
+      </c>
+      <c r="J26" t="str">
         <v>1000018001005</v>
       </c>
     </row>
@@ -1173,12 +1251,15 @@
         <v>49000</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>8</v>
-      </c>
-      <c r="I27" t="str">
+        <v>10</v>
+      </c>
+      <c r="I27">
+        <v>8</v>
+      </c>
+      <c r="J27" t="str">
         <v>1000046002517</v>
       </c>
     </row>
@@ -1202,12 +1283,15 @@
         <v>56000</v>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>8</v>
-      </c>
-      <c r="I28" t="str">
+        <v>10</v>
+      </c>
+      <c r="I28">
+        <v>8</v>
+      </c>
+      <c r="J28" t="str">
         <v>1000004000104</v>
       </c>
     </row>
@@ -1231,12 +1315,15 @@
         <v>60000</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>8</v>
-      </c>
-      <c r="I29" t="str">
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
+      <c r="J29" t="str">
         <v>1000018001012</v>
       </c>
     </row>
@@ -1260,12 +1347,15 @@
         <v>53000</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>8</v>
-      </c>
-      <c r="I30" t="str">
+        <v>10</v>
+      </c>
+      <c r="I30">
+        <v>8</v>
+      </c>
+      <c r="J30" t="str">
         <v>1000046002524</v>
       </c>
     </row>
@@ -1289,12 +1379,15 @@
         <v>50000</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>8</v>
-      </c>
-      <c r="I31" t="str">
+        <v>10</v>
+      </c>
+      <c r="I31">
+        <v>8</v>
+      </c>
+      <c r="J31" t="str">
         <v>1000004000081</v>
       </c>
     </row>
@@ -1318,12 +1411,15 @@
         <v>54000</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>8</v>
-      </c>
-      <c r="I32" t="str">
+        <v>10</v>
+      </c>
+      <c r="I32">
+        <v>8</v>
+      </c>
+      <c r="J32" t="str">
         <v>1000018000992</v>
       </c>
     </row>
@@ -1347,12 +1443,15 @@
         <v>48000</v>
       </c>
       <c r="G33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>8</v>
-      </c>
-      <c r="I33" t="str">
+        <v>10</v>
+      </c>
+      <c r="I33">
+        <v>8</v>
+      </c>
+      <c r="J33" t="str">
         <v>1000046002500</v>
       </c>
     </row>
@@ -1376,12 +1475,15 @@
         <v>66000</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>8</v>
-      </c>
-      <c r="I34" t="str">
+        <v>10</v>
+      </c>
+      <c r="I34">
+        <v>8</v>
+      </c>
+      <c r="J34" t="str">
         <v>1000004000111</v>
       </c>
     </row>
@@ -1405,12 +1507,15 @@
         <v>70000</v>
       </c>
       <c r="G35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>8</v>
-      </c>
-      <c r="I35" t="str">
+        <v>10</v>
+      </c>
+      <c r="I35">
+        <v>8</v>
+      </c>
+      <c r="J35" t="str">
         <v>1000018001029</v>
       </c>
     </row>
@@ -1434,12 +1539,15 @@
         <v>63000</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>8</v>
-      </c>
-      <c r="I36" t="str">
+        <v>10</v>
+      </c>
+      <c r="I36">
+        <v>8</v>
+      </c>
+      <c r="J36" t="str">
         <v>1000046002531</v>
       </c>
     </row>
@@ -1463,12 +1571,15 @@
         <v>55000</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>8</v>
-      </c>
-      <c r="I37" t="str">
+        <v>10</v>
+      </c>
+      <c r="I37">
+        <v>8</v>
+      </c>
+      <c r="J37" t="str">
         <v>1000005000134</v>
       </c>
     </row>
@@ -1492,12 +1603,15 @@
         <v>55000</v>
       </c>
       <c r="G38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>8</v>
-      </c>
-      <c r="I38" t="str">
+        <v>10</v>
+      </c>
+      <c r="I38">
+        <v>8</v>
+      </c>
+      <c r="J38" t="str">
         <v>1000019001042</v>
       </c>
     </row>
@@ -1521,12 +1635,15 @@
         <v>52000</v>
       </c>
       <c r="G39">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>8</v>
-      </c>
-      <c r="I39" t="str">
+        <v>10</v>
+      </c>
+      <c r="I39">
+        <v>8</v>
+      </c>
+      <c r="J39" t="str">
         <v>1000047002554</v>
       </c>
     </row>
@@ -1550,12 +1667,15 @@
         <v>58000</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>8</v>
-      </c>
-      <c r="I40" t="str">
+        <v>10</v>
+      </c>
+      <c r="I40">
+        <v>8</v>
+      </c>
+      <c r="J40" t="str">
         <v>1000005000141</v>
       </c>
     </row>
@@ -1579,12 +1699,15 @@
         <v>58000</v>
       </c>
       <c r="G41">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>8</v>
-      </c>
-      <c r="I41" t="str">
+        <v>10</v>
+      </c>
+      <c r="I41">
+        <v>8</v>
+      </c>
+      <c r="J41" t="str">
         <v>1000019001059</v>
       </c>
     </row>
@@ -1608,12 +1731,15 @@
         <v>55000</v>
       </c>
       <c r="G42">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>8</v>
-      </c>
-      <c r="I42" t="str">
+        <v>10</v>
+      </c>
+      <c r="I42">
+        <v>8</v>
+      </c>
+      <c r="J42" t="str">
         <v>1000047002561</v>
       </c>
     </row>
@@ -1637,12 +1763,15 @@
         <v>52000</v>
       </c>
       <c r="G43">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>8</v>
-      </c>
-      <c r="I43" t="str">
+        <v>10</v>
+      </c>
+      <c r="I43">
+        <v>8</v>
+      </c>
+      <c r="J43" t="str">
         <v>1000005000127</v>
       </c>
     </row>
@@ -1666,12 +1795,15 @@
         <v>52000</v>
       </c>
       <c r="G44">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>8</v>
-      </c>
-      <c r="I44" t="str">
+        <v>10</v>
+      </c>
+      <c r="I44">
+        <v>8</v>
+      </c>
+      <c r="J44" t="str">
         <v>1000019001035</v>
       </c>
     </row>
@@ -1695,12 +1827,15 @@
         <v>49000</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>8</v>
-      </c>
-      <c r="I45" t="str">
+        <v>10</v>
+      </c>
+      <c r="I45">
+        <v>8</v>
+      </c>
+      <c r="J45" t="str">
         <v>1000047002547</v>
       </c>
     </row>
@@ -1724,12 +1859,15 @@
         <v>62000</v>
       </c>
       <c r="G46">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>8</v>
-      </c>
-      <c r="I46" t="str">
+        <v>10</v>
+      </c>
+      <c r="I46">
+        <v>8</v>
+      </c>
+      <c r="J46" t="str">
         <v>1000005000165</v>
       </c>
     </row>
@@ -1753,12 +1891,15 @@
         <v>62000</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>8</v>
-      </c>
-      <c r="I47" t="str">
+        <v>10</v>
+      </c>
+      <c r="I47">
+        <v>8</v>
+      </c>
+      <c r="J47" t="str">
         <v>1000019001073</v>
       </c>
     </row>
@@ -1782,12 +1923,15 @@
         <v>59000</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>8</v>
-      </c>
-      <c r="I48" t="str">
+        <v>10</v>
+      </c>
+      <c r="I48">
+        <v>8</v>
+      </c>
+      <c r="J48" t="str">
         <v>1000047002585</v>
       </c>
     </row>
@@ -1811,12 +1955,15 @@
         <v>65000</v>
       </c>
       <c r="G49">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>8</v>
-      </c>
-      <c r="I49" t="str">
+        <v>10</v>
+      </c>
+      <c r="I49">
+        <v>8</v>
+      </c>
+      <c r="J49" t="str">
         <v>1000005000172</v>
       </c>
     </row>
@@ -1840,12 +1987,15 @@
         <v>65000</v>
       </c>
       <c r="G50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>8</v>
-      </c>
-      <c r="I50" t="str">
+        <v>10</v>
+      </c>
+      <c r="I50">
+        <v>8</v>
+      </c>
+      <c r="J50" t="str">
         <v>1000019001080</v>
       </c>
     </row>
@@ -1869,12 +2019,15 @@
         <v>60000</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>8</v>
-      </c>
-      <c r="I51" t="str">
+        <v>10</v>
+      </c>
+      <c r="I51">
+        <v>8</v>
+      </c>
+      <c r="J51" t="str">
         <v>1000047002592</v>
       </c>
     </row>
@@ -1898,12 +2051,15 @@
         <v>59000</v>
       </c>
       <c r="G52">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>8</v>
-      </c>
-      <c r="I52" t="str">
+        <v>10</v>
+      </c>
+      <c r="I52">
+        <v>8</v>
+      </c>
+      <c r="J52" t="str">
         <v>1000005000158</v>
       </c>
     </row>
@@ -1927,12 +2083,15 @@
         <v>59000</v>
       </c>
       <c r="G53">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>8</v>
-      </c>
-      <c r="I53" t="str">
+        <v>10</v>
+      </c>
+      <c r="I53">
+        <v>8</v>
+      </c>
+      <c r="J53" t="str">
         <v>1000019001066</v>
       </c>
     </row>
@@ -1956,12 +2115,15 @@
         <v>57000</v>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>8</v>
-      </c>
-      <c r="I54" t="str">
+        <v>10</v>
+      </c>
+      <c r="I54">
+        <v>8</v>
+      </c>
+      <c r="J54" t="str">
         <v>1000047002578</v>
       </c>
     </row>
@@ -1985,12 +2147,15 @@
         <v>66000</v>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>8</v>
-      </c>
-      <c r="I55" t="str">
+        <v>10</v>
+      </c>
+      <c r="I55">
+        <v>8</v>
+      </c>
+      <c r="J55" t="str">
         <v>1000005000189</v>
       </c>
     </row>
@@ -2014,12 +2179,15 @@
         <v>70000</v>
       </c>
       <c r="G56">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>8</v>
-      </c>
-      <c r="I56" t="str">
+        <v>10</v>
+      </c>
+      <c r="I56">
+        <v>8</v>
+      </c>
+      <c r="J56" t="str">
         <v>1000019001097</v>
       </c>
     </row>
@@ -2043,12 +2211,15 @@
         <v>68000</v>
       </c>
       <c r="G57">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>8</v>
-      </c>
-      <c r="I57" t="str">
+        <v>10</v>
+      </c>
+      <c r="I57">
+        <v>8</v>
+      </c>
+      <c r="J57" t="str">
         <v>1000047002608</v>
       </c>
     </row>
@@ -2072,12 +2243,15 @@
         <v>65000</v>
       </c>
       <c r="G58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>8</v>
-      </c>
-      <c r="I58" t="str">
+        <v>9</v>
+      </c>
+      <c r="I58">
+        <v>8</v>
+      </c>
+      <c r="J58" t="str">
         <v>1000015000834</v>
       </c>
     </row>
@@ -2101,12 +2275,15 @@
         <v>65000</v>
       </c>
       <c r="G59">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>8</v>
-      </c>
-      <c r="I59" t="str">
+        <v>10</v>
+      </c>
+      <c r="I59">
+        <v>8</v>
+      </c>
+      <c r="J59" t="str">
         <v>1000038002334</v>
       </c>
     </row>
@@ -2130,12 +2307,15 @@
         <v>69000</v>
       </c>
       <c r="G60">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>8</v>
-      </c>
-      <c r="I60" t="str">
+        <v>10</v>
+      </c>
+      <c r="I60">
+        <v>8</v>
+      </c>
+      <c r="J60" t="str">
         <v>1000015000841</v>
       </c>
     </row>
@@ -2159,12 +2339,15 @@
         <v>69000</v>
       </c>
       <c r="G61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>8</v>
-      </c>
-      <c r="I61" t="str">
+        <v>10</v>
+      </c>
+      <c r="I61">
+        <v>8</v>
+      </c>
+      <c r="J61" t="str">
         <v>1000038002341</v>
       </c>
     </row>
@@ -2188,12 +2371,15 @@
         <v>65000</v>
       </c>
       <c r="G62">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>8</v>
-      </c>
-      <c r="I62" t="str">
+        <v>10</v>
+      </c>
+      <c r="I62">
+        <v>8</v>
+      </c>
+      <c r="J62" t="str">
         <v>1000015000827</v>
       </c>
     </row>
@@ -2217,12 +2403,15 @@
         <v>65000</v>
       </c>
       <c r="G63">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>8</v>
-      </c>
-      <c r="I63" t="str">
+        <v>10</v>
+      </c>
+      <c r="I63">
+        <v>8</v>
+      </c>
+      <c r="J63" t="str">
         <v>1000038002327</v>
       </c>
     </row>
@@ -2246,12 +2435,15 @@
         <v>78000</v>
       </c>
       <c r="G64">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>8</v>
-      </c>
-      <c r="I64" t="str">
+        <v>9</v>
+      </c>
+      <c r="I64">
+        <v>8</v>
+      </c>
+      <c r="J64" t="str">
         <v>1000015000872</v>
       </c>
     </row>
@@ -2275,12 +2467,15 @@
         <v>78000</v>
       </c>
       <c r="G65">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>8</v>
-      </c>
-      <c r="I65" t="str">
+        <v>10</v>
+      </c>
+      <c r="I65">
+        <v>8</v>
+      </c>
+      <c r="J65" t="str">
         <v>1000038002372</v>
       </c>
     </row>
@@ -2304,12 +2499,15 @@
         <v>70000</v>
       </c>
       <c r="G66">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>8</v>
-      </c>
-      <c r="I66" t="str">
+        <v>10</v>
+      </c>
+      <c r="I66">
+        <v>8</v>
+      </c>
+      <c r="J66" t="str">
         <v>1000015000865</v>
       </c>
     </row>
@@ -2333,12 +2531,15 @@
         <v>70000</v>
       </c>
       <c r="G67">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>8</v>
-      </c>
-      <c r="I67" t="str">
+        <v>10</v>
+      </c>
+      <c r="I67">
+        <v>8</v>
+      </c>
+      <c r="J67" t="str">
         <v>1000038002365</v>
       </c>
     </row>
@@ -2362,12 +2563,15 @@
         <v>69000</v>
       </c>
       <c r="G68">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>8</v>
-      </c>
-      <c r="I68" t="str">
+        <v>10</v>
+      </c>
+      <c r="I68">
+        <v>8</v>
+      </c>
+      <c r="J68" t="str">
         <v>1000015000858</v>
       </c>
     </row>
@@ -2391,12 +2595,15 @@
         <v>69000</v>
       </c>
       <c r="G69">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>8</v>
-      </c>
-      <c r="I69" t="str">
+        <v>9</v>
+      </c>
+      <c r="I69">
+        <v>8</v>
+      </c>
+      <c r="J69" t="str">
         <v>1000038002358</v>
       </c>
     </row>
@@ -2420,12 +2627,15 @@
         <v>54000</v>
       </c>
       <c r="G70">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>8</v>
-      </c>
-      <c r="I70" t="str">
+        <v>10</v>
+      </c>
+      <c r="I70">
+        <v>8</v>
+      </c>
+      <c r="J70" t="str">
         <v>1000030001731</v>
       </c>
     </row>
@@ -2449,12 +2659,15 @@
         <v>57000</v>
       </c>
       <c r="G71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>8</v>
-      </c>
-      <c r="I71" t="str">
+        <v>10</v>
+      </c>
+      <c r="I71">
+        <v>8</v>
+      </c>
+      <c r="J71" t="str">
         <v>1000030001748</v>
       </c>
     </row>
@@ -2478,12 +2691,15 @@
         <v>50000</v>
       </c>
       <c r="G72">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>8</v>
-      </c>
-      <c r="I72" t="str">
+        <v>10</v>
+      </c>
+      <c r="I72">
+        <v>8</v>
+      </c>
+      <c r="J72" t="str">
         <v>1000030001724</v>
       </c>
     </row>
@@ -2507,12 +2723,15 @@
         <v>63000</v>
       </c>
       <c r="G73">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>8</v>
-      </c>
-      <c r="I73" t="str">
+        <v>10</v>
+      </c>
+      <c r="I73">
+        <v>8</v>
+      </c>
+      <c r="J73" t="str">
         <v>1000030001762</v>
       </c>
     </row>
@@ -2536,12 +2755,15 @@
         <v>65000</v>
       </c>
       <c r="G74">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>8</v>
-      </c>
-      <c r="I74" t="str">
+        <v>10</v>
+      </c>
+      <c r="I74">
+        <v>8</v>
+      </c>
+      <c r="J74" t="str">
         <v>1000030001779</v>
       </c>
     </row>
@@ -2565,12 +2787,15 @@
         <v>60000</v>
       </c>
       <c r="G75">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>8</v>
-      </c>
-      <c r="I75" t="str">
+        <v>10</v>
+      </c>
+      <c r="I75">
+        <v>8</v>
+      </c>
+      <c r="J75" t="str">
         <v>1000030001755</v>
       </c>
     </row>
@@ -2594,12 +2819,15 @@
         <v>63000</v>
       </c>
       <c r="G76">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>8</v>
-      </c>
-      <c r="I76" t="str">
+        <v>10</v>
+      </c>
+      <c r="I76">
+        <v>8</v>
+      </c>
+      <c r="J76" t="str">
         <v>1000031001792</v>
       </c>
     </row>
@@ -2623,12 +2851,15 @@
         <v>66000</v>
       </c>
       <c r="G77">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H77">
-        <v>8</v>
-      </c>
-      <c r="I77" t="str">
+        <v>10</v>
+      </c>
+      <c r="I77">
+        <v>8</v>
+      </c>
+      <c r="J77" t="str">
         <v>1000031001808</v>
       </c>
     </row>
@@ -2652,12 +2883,15 @@
         <v>60000</v>
       </c>
       <c r="G78">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H78">
-        <v>8</v>
-      </c>
-      <c r="I78" t="str">
+        <v>10</v>
+      </c>
+      <c r="I78">
+        <v>8</v>
+      </c>
+      <c r="J78" t="str">
         <v>1000031001785</v>
       </c>
     </row>
@@ -2681,12 +2915,15 @@
         <v>75000</v>
       </c>
       <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
         <v>15</v>
       </c>
-      <c r="H79">
-        <v>8</v>
-      </c>
-      <c r="I79" t="str">
+      <c r="I79">
+        <v>8</v>
+      </c>
+      <c r="J79" t="str">
         <v>1000031001822</v>
       </c>
     </row>
@@ -2710,12 +2947,15 @@
         <v>78000</v>
       </c>
       <c r="G80">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H80">
-        <v>8</v>
-      </c>
-      <c r="I80" t="str">
+        <v>10</v>
+      </c>
+      <c r="I80">
+        <v>8</v>
+      </c>
+      <c r="J80" t="str">
         <v>1000031001839</v>
       </c>
     </row>
@@ -2739,12 +2979,15 @@
         <v>69000</v>
       </c>
       <c r="G81">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>8</v>
-      </c>
-      <c r="I81" t="str">
+        <v>10</v>
+      </c>
+      <c r="I81">
+        <v>8</v>
+      </c>
+      <c r="J81" t="str">
         <v>1000031001815</v>
       </c>
     </row>
@@ -2768,12 +3011,15 @@
         <v>15000</v>
       </c>
       <c r="G82">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>8</v>
-      </c>
-      <c r="I82" t="str">
+        <v>10</v>
+      </c>
+      <c r="I82">
+        <v>8</v>
+      </c>
+      <c r="J82" t="str">
         <v>1000044002458</v>
       </c>
     </row>
@@ -2797,12 +3043,15 @@
         <v>12000</v>
       </c>
       <c r="G83">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>8</v>
-      </c>
-      <c r="I83" t="str">
+        <v>10</v>
+      </c>
+      <c r="I83">
+        <v>8</v>
+      </c>
+      <c r="J83" t="str">
         <v>1000043002442</v>
       </c>
     </row>
@@ -2826,12 +3075,15 @@
         <v>15000</v>
       </c>
       <c r="G84">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>8</v>
-      </c>
-      <c r="I84" t="str">
+        <v>10</v>
+      </c>
+      <c r="I84">
+        <v>8</v>
+      </c>
+      <c r="J84" t="str">
         <v>1000045002464</v>
       </c>
     </row>
@@ -2855,12 +3107,15 @@
         <v>22000</v>
       </c>
       <c r="G85">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>8</v>
-      </c>
-      <c r="I85" t="str">
+        <v>10</v>
+      </c>
+      <c r="I85">
+        <v>8</v>
+      </c>
+      <c r="J85" t="str">
         <v>1000028001705</v>
       </c>
     </row>
@@ -2884,12 +3139,15 @@
         <v>22000</v>
       </c>
       <c r="G86">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>8</v>
-      </c>
-      <c r="I86" t="str">
+        <v>10</v>
+      </c>
+      <c r="I86">
+        <v>8</v>
+      </c>
+      <c r="J86" t="str">
         <v>1000041002420</v>
       </c>
     </row>
@@ -2913,12 +3171,15 @@
         <v>15000</v>
       </c>
       <c r="G87">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>8</v>
-      </c>
-      <c r="I87" t="str">
+        <v>10</v>
+      </c>
+      <c r="I87">
+        <v>8</v>
+      </c>
+      <c r="J87" t="str">
         <v>1000029001711</v>
       </c>
     </row>
@@ -2942,12 +3203,15 @@
         <v>15000</v>
       </c>
       <c r="G88">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>8</v>
-      </c>
-      <c r="I88" t="str">
+        <v>10</v>
+      </c>
+      <c r="I88">
+        <v>8</v>
+      </c>
+      <c r="J88" t="str">
         <v>1000042002436</v>
       </c>
     </row>
@@ -2971,12 +3235,15 @@
         <v>56000</v>
       </c>
       <c r="G89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>8</v>
-      </c>
-      <c r="I89" t="str">
+        <v>10</v>
+      </c>
+      <c r="I89">
+        <v>8</v>
+      </c>
+      <c r="J89" t="str">
         <v>1000008000346</v>
       </c>
     </row>
@@ -3000,12 +3267,15 @@
         <v>76000</v>
       </c>
       <c r="G90">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>8</v>
-      </c>
-      <c r="I90" t="str">
+        <v>10</v>
+      </c>
+      <c r="I90">
+        <v>8</v>
+      </c>
+      <c r="J90" t="str">
         <v>1000022001251</v>
       </c>
     </row>
@@ -3029,12 +3299,15 @@
         <v>45000</v>
       </c>
       <c r="G91">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>8</v>
-      </c>
-      <c r="I91" t="str">
+        <v>10</v>
+      </c>
+      <c r="I91">
+        <v>8</v>
+      </c>
+      <c r="J91" t="str">
         <v>1000032001852</v>
       </c>
     </row>
@@ -3058,12 +3331,15 @@
         <v>60000</v>
       </c>
       <c r="G92">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>8</v>
-      </c>
-      <c r="I92" t="str">
+        <v>10</v>
+      </c>
+      <c r="I92">
+        <v>8</v>
+      </c>
+      <c r="J92" t="str">
         <v>1000008000353</v>
       </c>
     </row>
@@ -3087,12 +3363,15 @@
         <v>79000</v>
       </c>
       <c r="G93">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>8</v>
-      </c>
-      <c r="I93" t="str">
+        <v>10</v>
+      </c>
+      <c r="I93">
+        <v>8</v>
+      </c>
+      <c r="J93" t="str">
         <v>1000022001268</v>
       </c>
     </row>
@@ -3116,12 +3395,15 @@
         <v>48000</v>
       </c>
       <c r="G94">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H94">
-        <v>8</v>
-      </c>
-      <c r="I94" t="str">
+        <v>10</v>
+      </c>
+      <c r="I94">
+        <v>8</v>
+      </c>
+      <c r="J94" t="str">
         <v>1000032001869</v>
       </c>
     </row>
@@ -3145,12 +3427,15 @@
         <v>54000</v>
       </c>
       <c r="G95">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>8</v>
-      </c>
-      <c r="I95" t="str">
+        <v>10</v>
+      </c>
+      <c r="I95">
+        <v>8</v>
+      </c>
+      <c r="J95" t="str">
         <v>1000008000339</v>
       </c>
     </row>
@@ -3174,12 +3459,15 @@
         <v>67000</v>
       </c>
       <c r="G96">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>8</v>
-      </c>
-      <c r="I96" t="str">
+        <v>10</v>
+      </c>
+      <c r="I96">
+        <v>8</v>
+      </c>
+      <c r="J96" t="str">
         <v>1000022001244</v>
       </c>
     </row>
@@ -3203,12 +3491,15 @@
         <v>43000</v>
       </c>
       <c r="G97">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>8</v>
-      </c>
-      <c r="I97" t="str">
+        <v>10</v>
+      </c>
+      <c r="I97">
+        <v>8</v>
+      </c>
+      <c r="J97" t="str">
         <v>1000032001845</v>
       </c>
     </row>
@@ -3232,12 +3523,15 @@
         <v>68000</v>
       </c>
       <c r="G98">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>8</v>
-      </c>
-      <c r="I98" t="str">
+        <v>10</v>
+      </c>
+      <c r="I98">
+        <v>8</v>
+      </c>
+      <c r="J98" t="str">
         <v>1000008000384</v>
       </c>
     </row>
@@ -3261,12 +3555,15 @@
         <v>85000</v>
       </c>
       <c r="G99">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>8</v>
-      </c>
-      <c r="I99" t="str">
+        <v>10</v>
+      </c>
+      <c r="I99">
+        <v>8</v>
+      </c>
+      <c r="J99" t="str">
         <v>1000022001299</v>
       </c>
     </row>
@@ -3290,12 +3587,15 @@
         <v>57000</v>
       </c>
       <c r="G100">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>8</v>
-      </c>
-      <c r="I100" t="str">
+        <v>10</v>
+      </c>
+      <c r="I100">
+        <v>8</v>
+      </c>
+      <c r="J100" t="str">
         <v>1000032001890</v>
       </c>
     </row>
@@ -3319,12 +3619,15 @@
         <v>66000</v>
       </c>
       <c r="G101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>8</v>
-      </c>
-      <c r="I101" t="str">
+        <v>10</v>
+      </c>
+      <c r="I101">
+        <v>8</v>
+      </c>
+      <c r="J101" t="str">
         <v>1000008000377</v>
       </c>
     </row>
@@ -3348,12 +3651,15 @@
         <v>83000</v>
       </c>
       <c r="G102">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>8</v>
-      </c>
-      <c r="I102" t="str">
+        <v>10</v>
+      </c>
+      <c r="I102">
+        <v>8</v>
+      </c>
+      <c r="J102" t="str">
         <v>1000022001282</v>
       </c>
     </row>
@@ -3377,12 +3683,15 @@
         <v>55000</v>
       </c>
       <c r="G103">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H103">
-        <v>8</v>
-      </c>
-      <c r="I103" t="str">
+        <v>10</v>
+      </c>
+      <c r="I103">
+        <v>8</v>
+      </c>
+      <c r="J103" t="str">
         <v>1000032001883</v>
       </c>
     </row>
@@ -3406,12 +3715,15 @@
         <v>64000</v>
       </c>
       <c r="G104">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H104">
-        <v>8</v>
-      </c>
-      <c r="I104" t="str">
+        <v>10</v>
+      </c>
+      <c r="I104">
+        <v>8</v>
+      </c>
+      <c r="J104" t="str">
         <v>1000008000360</v>
       </c>
     </row>
@@ -3435,12 +3747,15 @@
         <v>82000</v>
       </c>
       <c r="G105">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>8</v>
-      </c>
-      <c r="I105" t="str">
+        <v>10</v>
+      </c>
+      <c r="I105">
+        <v>8</v>
+      </c>
+      <c r="J105" t="str">
         <v>1000022001275</v>
       </c>
     </row>
@@ -3464,12 +3779,15 @@
         <v>52000</v>
       </c>
       <c r="G106">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H106">
-        <v>8</v>
-      </c>
-      <c r="I106" t="str">
+        <v>10</v>
+      </c>
+      <c r="I106">
+        <v>8</v>
+      </c>
+      <c r="J106" t="str">
         <v>1000032001876</v>
       </c>
     </row>
@@ -3493,12 +3811,15 @@
         <v>74000</v>
       </c>
       <c r="G107">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>8</v>
-      </c>
-      <c r="I107" t="str">
+        <v>10</v>
+      </c>
+      <c r="I107">
+        <v>8</v>
+      </c>
+      <c r="J107" t="str">
         <v>1000008000391</v>
       </c>
     </row>
@@ -3522,12 +3843,15 @@
         <v>90000</v>
       </c>
       <c r="G108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>8</v>
-      </c>
-      <c r="I108" t="str">
+        <v>10</v>
+      </c>
+      <c r="I108">
+        <v>8</v>
+      </c>
+      <c r="J108" t="str">
         <v>1000022001305</v>
       </c>
     </row>
@@ -3551,12 +3875,15 @@
         <v>58000</v>
       </c>
       <c r="G109">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>8</v>
-      </c>
-      <c r="I109" t="str">
+        <v>10</v>
+      </c>
+      <c r="I109">
+        <v>8</v>
+      </c>
+      <c r="J109" t="str">
         <v>1000032001906</v>
       </c>
     </row>
@@ -3580,12 +3907,15 @@
         <v>62000</v>
       </c>
       <c r="G110">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>8</v>
-      </c>
-      <c r="I110" t="str">
+        <v>10</v>
+      </c>
+      <c r="I110">
+        <v>8</v>
+      </c>
+      <c r="J110" t="str">
         <v>1000032001913</v>
       </c>
     </row>
@@ -3609,12 +3939,15 @@
         <v>57000</v>
       </c>
       <c r="G111">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H111">
-        <v>8</v>
-      </c>
-      <c r="I111" t="str">
+        <v>10</v>
+      </c>
+      <c r="I111">
+        <v>8</v>
+      </c>
+      <c r="J111" t="str">
         <v>1000006000201</v>
       </c>
     </row>
@@ -3638,12 +3971,15 @@
         <v>57000</v>
       </c>
       <c r="G112">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>8</v>
-      </c>
-      <c r="I112" t="str">
+        <v>10</v>
+      </c>
+      <c r="I112">
+        <v>8</v>
+      </c>
+      <c r="J112" t="str">
         <v>1000020001116</v>
       </c>
     </row>
@@ -3667,12 +4003,15 @@
         <v>57000</v>
       </c>
       <c r="G113">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>8</v>
-      </c>
-      <c r="I113" t="str">
+        <v>10</v>
+      </c>
+      <c r="I113">
+        <v>8</v>
+      </c>
+      <c r="J113" t="str">
         <v>1000048002621</v>
       </c>
     </row>
@@ -3696,12 +4035,15 @@
         <v>59000</v>
       </c>
       <c r="G114">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>8</v>
-      </c>
-      <c r="I114" t="str">
+        <v>10</v>
+      </c>
+      <c r="I114">
+        <v>8</v>
+      </c>
+      <c r="J114" t="str">
         <v>1000006000218</v>
       </c>
     </row>
@@ -3725,12 +4067,15 @@
         <v>59000</v>
       </c>
       <c r="G115">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>8</v>
-      </c>
-      <c r="I115" t="str">
+        <v>10</v>
+      </c>
+      <c r="I115">
+        <v>8</v>
+      </c>
+      <c r="J115" t="str">
         <v>1000020001123</v>
       </c>
     </row>
@@ -3754,12 +4099,15 @@
         <v>59000</v>
       </c>
       <c r="G116">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>8</v>
-      </c>
-      <c r="I116" t="str">
+        <v>10</v>
+      </c>
+      <c r="I116">
+        <v>8</v>
+      </c>
+      <c r="J116" t="str">
         <v>1000048002638</v>
       </c>
     </row>
@@ -3783,12 +4131,15 @@
         <v>53000</v>
       </c>
       <c r="G117">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>8</v>
-      </c>
-      <c r="I117" t="str">
+        <v>10</v>
+      </c>
+      <c r="I117">
+        <v>8</v>
+      </c>
+      <c r="J117" t="str">
         <v>1000006000195</v>
       </c>
     </row>
@@ -3812,12 +4163,15 @@
         <v>53000</v>
       </c>
       <c r="G118">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>8</v>
-      </c>
-      <c r="I118" t="str">
+        <v>10</v>
+      </c>
+      <c r="I118">
+        <v>8</v>
+      </c>
+      <c r="J118" t="str">
         <v>1000020001109</v>
       </c>
     </row>
@@ -3841,12 +4195,15 @@
         <v>53000</v>
       </c>
       <c r="G119">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>8</v>
-      </c>
-      <c r="I119" t="str">
+        <v>10</v>
+      </c>
+      <c r="I119">
+        <v>8</v>
+      </c>
+      <c r="J119" t="str">
         <v>1000048002614</v>
       </c>
     </row>
@@ -3870,12 +4227,15 @@
         <v>64000</v>
       </c>
       <c r="G120">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H120">
-        <v>8</v>
-      </c>
-      <c r="I120" t="str">
+        <v>9</v>
+      </c>
+      <c r="I120">
+        <v>8</v>
+      </c>
+      <c r="J120" t="str">
         <v>1000006000232</v>
       </c>
     </row>
@@ -3899,12 +4259,15 @@
         <v>64000</v>
       </c>
       <c r="G121">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>8</v>
-      </c>
-      <c r="I121" t="str">
+        <v>10</v>
+      </c>
+      <c r="I121">
+        <v>8</v>
+      </c>
+      <c r="J121" t="str">
         <v>1000020001147</v>
       </c>
     </row>
@@ -3928,12 +4291,15 @@
         <v>64000</v>
       </c>
       <c r="G122">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>8</v>
-      </c>
-      <c r="I122" t="str">
+        <v>10</v>
+      </c>
+      <c r="I122">
+        <v>8</v>
+      </c>
+      <c r="J122" t="str">
         <v>1000048002652</v>
       </c>
     </row>
@@ -3957,12 +4323,15 @@
         <v>66000</v>
       </c>
       <c r="G123">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>8</v>
-      </c>
-      <c r="I123" t="str">
+        <v>10</v>
+      </c>
+      <c r="I123">
+        <v>8</v>
+      </c>
+      <c r="J123" t="str">
         <v>1000006000249</v>
       </c>
     </row>
@@ -3986,12 +4355,15 @@
         <v>66000</v>
       </c>
       <c r="G124">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>8</v>
-      </c>
-      <c r="I124" t="str">
+        <v>10</v>
+      </c>
+      <c r="I124">
+        <v>8</v>
+      </c>
+      <c r="J124" t="str">
         <v>1000020001154</v>
       </c>
     </row>
@@ -4015,12 +4387,15 @@
         <v>66000</v>
       </c>
       <c r="G125">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>8</v>
-      </c>
-      <c r="I125" t="str">
+        <v>10</v>
+      </c>
+      <c r="I125">
+        <v>8</v>
+      </c>
+      <c r="J125" t="str">
         <v>1000048002669</v>
       </c>
     </row>
@@ -4044,12 +4419,15 @@
         <v>62000</v>
       </c>
       <c r="G126">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>8</v>
-      </c>
-      <c r="I126" t="str">
+        <v>10</v>
+      </c>
+      <c r="I126">
+        <v>8</v>
+      </c>
+      <c r="J126" t="str">
         <v>1000006000225</v>
       </c>
     </row>
@@ -4073,12 +4451,15 @@
         <v>62000</v>
       </c>
       <c r="G127">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>8</v>
-      </c>
-      <c r="I127" t="str">
+        <v>10</v>
+      </c>
+      <c r="I127">
+        <v>8</v>
+      </c>
+      <c r="J127" t="str">
         <v>1000020001130</v>
       </c>
     </row>
@@ -4102,12 +4483,15 @@
         <v>62000</v>
       </c>
       <c r="G128">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>8</v>
-      </c>
-      <c r="I128" t="str">
+        <v>10</v>
+      </c>
+      <c r="I128">
+        <v>8</v>
+      </c>
+      <c r="J128" t="str">
         <v>1000048002645</v>
       </c>
     </row>
@@ -4131,12 +4515,15 @@
         <v>70000</v>
       </c>
       <c r="G129">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>8</v>
-      </c>
-      <c r="I129" t="str">
+        <v>10</v>
+      </c>
+      <c r="I129">
+        <v>8</v>
+      </c>
+      <c r="J129" t="str">
         <v>1000006000256</v>
       </c>
     </row>
@@ -4160,12 +4547,15 @@
         <v>70000</v>
       </c>
       <c r="G130">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>8</v>
-      </c>
-      <c r="I130" t="str">
+        <v>10</v>
+      </c>
+      <c r="I130">
+        <v>8</v>
+      </c>
+      <c r="J130" t="str">
         <v>1000020001161</v>
       </c>
     </row>
@@ -4189,12 +4579,15 @@
         <v>70000</v>
       </c>
       <c r="G131">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>8</v>
-      </c>
-      <c r="I131" t="str">
+        <v>10</v>
+      </c>
+      <c r="I131">
+        <v>8</v>
+      </c>
+      <c r="J131" t="str">
         <v>1000048002676</v>
       </c>
     </row>
@@ -4218,12 +4611,15 @@
         <v>54000</v>
       </c>
       <c r="G132">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H132">
-        <v>8</v>
-      </c>
-      <c r="I132" t="str">
+        <v>10</v>
+      </c>
+      <c r="I132">
+        <v>8</v>
+      </c>
+      <c r="J132" t="str">
         <v>1000007000279</v>
       </c>
     </row>
@@ -4247,12 +4643,15 @@
         <v>62000</v>
       </c>
       <c r="G133">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H133">
-        <v>8</v>
-      </c>
-      <c r="I133" t="str">
+        <v>10</v>
+      </c>
+      <c r="I133">
+        <v>8</v>
+      </c>
+      <c r="J133" t="str">
         <v>1000021001184</v>
       </c>
     </row>
@@ -4276,12 +4675,15 @@
         <v>62000</v>
       </c>
       <c r="G134">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>8</v>
-      </c>
-      <c r="I134" t="str">
+        <v>10</v>
+      </c>
+      <c r="I134">
+        <v>8</v>
+      </c>
+      <c r="J134" t="str">
         <v>1000049002699</v>
       </c>
     </row>
@@ -4305,12 +4707,15 @@
         <v>55000</v>
       </c>
       <c r="G135">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>8</v>
-      </c>
-      <c r="I135" t="str">
+        <v>10</v>
+      </c>
+      <c r="I135">
+        <v>8</v>
+      </c>
+      <c r="J135" t="str">
         <v>1000007000286</v>
       </c>
     </row>
@@ -4334,12 +4739,15 @@
         <v>64000</v>
       </c>
       <c r="G136">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H136">
-        <v>8</v>
-      </c>
-      <c r="I136" t="str">
+        <v>10</v>
+      </c>
+      <c r="I136">
+        <v>8</v>
+      </c>
+      <c r="J136" t="str">
         <v>1000021001191</v>
       </c>
     </row>
@@ -4363,12 +4771,15 @@
         <v>64000</v>
       </c>
       <c r="G137">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H137">
-        <v>8</v>
-      </c>
-      <c r="I137" t="str">
+        <v>10</v>
+      </c>
+      <c r="I137">
+        <v>8</v>
+      </c>
+      <c r="J137" t="str">
         <v>1000049002705</v>
       </c>
     </row>
@@ -4392,12 +4803,15 @@
         <v>54000</v>
       </c>
       <c r="G138">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H138">
-        <v>8</v>
-      </c>
-      <c r="I138" t="str">
+        <v>10</v>
+      </c>
+      <c r="I138">
+        <v>8</v>
+      </c>
+      <c r="J138" t="str">
         <v>1000007000262</v>
       </c>
     </row>
@@ -4421,12 +4835,15 @@
         <v>59000</v>
       </c>
       <c r="G139">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>8</v>
-      </c>
-      <c r="I139" t="str">
+        <v>10</v>
+      </c>
+      <c r="I139">
+        <v>8</v>
+      </c>
+      <c r="J139" t="str">
         <v>1000021001177</v>
       </c>
     </row>
@@ -4450,12 +4867,15 @@
         <v>59000</v>
       </c>
       <c r="G140">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H140">
-        <v>8</v>
-      </c>
-      <c r="I140" t="str">
+        <v>10</v>
+      </c>
+      <c r="I140">
+        <v>8</v>
+      </c>
+      <c r="J140" t="str">
         <v>1000049002682</v>
       </c>
     </row>
@@ -4479,12 +4899,15 @@
         <v>62000</v>
       </c>
       <c r="G141">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>8</v>
-      </c>
-      <c r="I141" t="str">
+        <v>10</v>
+      </c>
+      <c r="I141">
+        <v>8</v>
+      </c>
+      <c r="J141" t="str">
         <v>1000007000309</v>
       </c>
     </row>
@@ -4508,12 +4931,15 @@
         <v>69000</v>
       </c>
       <c r="G142">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H142">
-        <v>8</v>
-      </c>
-      <c r="I142" t="str">
+        <v>10</v>
+      </c>
+      <c r="I142">
+        <v>8</v>
+      </c>
+      <c r="J142" t="str">
         <v>1000021001214</v>
       </c>
     </row>
@@ -4537,12 +4963,15 @@
         <v>69000</v>
       </c>
       <c r="G143">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>8</v>
-      </c>
-      <c r="I143" t="str">
+        <v>10</v>
+      </c>
+      <c r="I143">
+        <v>8</v>
+      </c>
+      <c r="J143" t="str">
         <v>1000049002729</v>
       </c>
     </row>
@@ -4566,12 +4995,15 @@
         <v>62000</v>
       </c>
       <c r="G144">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>8</v>
-      </c>
-      <c r="I144" t="str">
+        <v>10</v>
+      </c>
+      <c r="I144">
+        <v>8</v>
+      </c>
+      <c r="J144" t="str">
         <v>1000007000316</v>
       </c>
     </row>
@@ -4595,12 +5027,15 @@
         <v>70000</v>
       </c>
       <c r="G145">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>8</v>
-      </c>
-      <c r="I145" t="str">
+        <v>10</v>
+      </c>
+      <c r="I145">
+        <v>8</v>
+      </c>
+      <c r="J145" t="str">
         <v>1000021001221</v>
       </c>
     </row>
@@ -4624,12 +5059,15 @@
         <v>70000</v>
       </c>
       <c r="G146">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>8</v>
-      </c>
-      <c r="I146" t="str">
+        <v>10</v>
+      </c>
+      <c r="I146">
+        <v>8</v>
+      </c>
+      <c r="J146" t="str">
         <v>1000049002736</v>
       </c>
     </row>
@@ -4653,12 +5091,15 @@
         <v>62000</v>
       </c>
       <c r="G147">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>8</v>
-      </c>
-      <c r="I147" t="str">
+        <v>10</v>
+      </c>
+      <c r="I147">
+        <v>8</v>
+      </c>
+      <c r="J147" t="str">
         <v>1000007000293</v>
       </c>
     </row>
@@ -4682,12 +5123,15 @@
         <v>67000</v>
       </c>
       <c r="G148">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H148">
-        <v>8</v>
-      </c>
-      <c r="I148" t="str">
+        <v>10</v>
+      </c>
+      <c r="I148">
+        <v>8</v>
+      </c>
+      <c r="J148" t="str">
         <v>1000021001207</v>
       </c>
     </row>
@@ -4711,12 +5155,15 @@
         <v>67000</v>
       </c>
       <c r="G149">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>8</v>
-      </c>
-      <c r="I149" t="str">
+        <v>10</v>
+      </c>
+      <c r="I149">
+        <v>8</v>
+      </c>
+      <c r="J149" t="str">
         <v>1000049002712</v>
       </c>
     </row>
@@ -4740,12 +5187,15 @@
         <v>65000</v>
       </c>
       <c r="G150">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H150">
-        <v>8</v>
-      </c>
-      <c r="I150" t="str">
+        <v>10</v>
+      </c>
+      <c r="I150">
+        <v>8</v>
+      </c>
+      <c r="J150" t="str">
         <v>1000007000323</v>
       </c>
     </row>
@@ -4769,12 +5219,15 @@
         <v>75000</v>
       </c>
       <c r="G151">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>8</v>
-      </c>
-      <c r="I151" t="str">
+        <v>10</v>
+      </c>
+      <c r="I151">
+        <v>8</v>
+      </c>
+      <c r="J151" t="str">
         <v>1000021001238</v>
       </c>
     </row>
@@ -4798,12 +5251,15 @@
         <v>75000</v>
       </c>
       <c r="G152">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H152">
-        <v>8</v>
-      </c>
-      <c r="I152" t="str">
+        <v>10</v>
+      </c>
+      <c r="I152">
+        <v>8</v>
+      </c>
+      <c r="J152" t="str">
         <v>1000049002743</v>
       </c>
     </row>
@@ -4827,12 +5283,15 @@
         <v>96000</v>
       </c>
       <c r="G153">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>8</v>
-      </c>
-      <c r="I153" t="str">
+        <v>10</v>
+      </c>
+      <c r="I153">
+        <v>8</v>
+      </c>
+      <c r="J153" t="str">
         <v>1000050002763</v>
       </c>
     </row>
@@ -4856,12 +5315,15 @@
         <v>98000</v>
       </c>
       <c r="G154">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>8</v>
-      </c>
-      <c r="I154" t="str">
+        <v>10</v>
+      </c>
+      <c r="I154">
+        <v>8</v>
+      </c>
+      <c r="J154" t="str">
         <v>1000050002770</v>
       </c>
     </row>
@@ -4885,12 +5347,15 @@
         <v>99000</v>
       </c>
       <c r="G155">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>8</v>
-      </c>
-      <c r="I155" t="str">
+        <v>10</v>
+      </c>
+      <c r="I155">
+        <v>8</v>
+      </c>
+      <c r="J155" t="str">
         <v>1000050002787</v>
       </c>
     </row>
@@ -4914,12 +5379,15 @@
         <v>102000</v>
       </c>
       <c r="G156">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>8</v>
-      </c>
-      <c r="I156" t="str">
+        <v>10</v>
+      </c>
+      <c r="I156">
+        <v>8</v>
+      </c>
+      <c r="J156" t="str">
         <v>1000050002794</v>
       </c>
     </row>
@@ -4943,12 +5411,15 @@
         <v>90000</v>
       </c>
       <c r="G157">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>8</v>
-      </c>
-      <c r="I157" t="str">
+        <v>10</v>
+      </c>
+      <c r="I157">
+        <v>8</v>
+      </c>
+      <c r="J157" t="str">
         <v>1000050002756</v>
       </c>
     </row>
@@ -4972,12 +5443,15 @@
         <v>115000</v>
       </c>
       <c r="G158">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>8</v>
-      </c>
-      <c r="I158" t="str">
+        <v>10</v>
+      </c>
+      <c r="I158">
+        <v>8</v>
+      </c>
+      <c r="J158" t="str">
         <v>1000050002824</v>
       </c>
     </row>
@@ -5001,12 +5475,15 @@
         <v>112000</v>
       </c>
       <c r="G159">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>8</v>
-      </c>
-      <c r="I159" t="str">
+        <v>10</v>
+      </c>
+      <c r="I159">
+        <v>8</v>
+      </c>
+      <c r="J159" t="str">
         <v>1000050002817</v>
       </c>
     </row>
@@ -5030,12 +5507,15 @@
         <v>112000</v>
       </c>
       <c r="G160">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H160">
-        <v>8</v>
-      </c>
-      <c r="I160" t="str">
+        <v>10</v>
+      </c>
+      <c r="I160">
+        <v>8</v>
+      </c>
+      <c r="J160" t="str">
         <v>1000050002800</v>
       </c>
     </row>
@@ -5059,12 +5539,15 @@
         <v>76000</v>
       </c>
       <c r="G161">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>8</v>
-      </c>
-      <c r="I161" t="str">
+        <v>10</v>
+      </c>
+      <c r="I161">
+        <v>8</v>
+      </c>
+      <c r="J161" t="str">
         <v>1000023001328</v>
       </c>
     </row>
@@ -5088,12 +5571,15 @@
         <v>76000</v>
       </c>
       <c r="G162">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>8</v>
-      </c>
-      <c r="I162" t="str">
+        <v>10</v>
+      </c>
+      <c r="I162">
+        <v>8</v>
+      </c>
+      <c r="J162" t="str">
         <v>1000051002847</v>
       </c>
     </row>
@@ -5117,12 +5603,15 @@
         <v>79000</v>
       </c>
       <c r="G163">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>8</v>
-      </c>
-      <c r="I163" t="str">
+        <v>10</v>
+      </c>
+      <c r="I163">
+        <v>8</v>
+      </c>
+      <c r="J163" t="str">
         <v>1000023001335</v>
       </c>
     </row>
@@ -5146,12 +5635,15 @@
         <v>79000</v>
       </c>
       <c r="G164">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>8</v>
-      </c>
-      <c r="I164" t="str">
+        <v>10</v>
+      </c>
+      <c r="I164">
+        <v>8</v>
+      </c>
+      <c r="J164" t="str">
         <v>1000051002854</v>
       </c>
     </row>
@@ -5175,12 +5667,15 @@
         <v>82000</v>
       </c>
       <c r="G165">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>8</v>
-      </c>
-      <c r="I165" t="str">
+        <v>10</v>
+      </c>
+      <c r="I165">
+        <v>8</v>
+      </c>
+      <c r="J165" t="str">
         <v>1000023001342</v>
       </c>
     </row>
@@ -5204,12 +5699,15 @@
         <v>82000</v>
       </c>
       <c r="G166">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>8</v>
-      </c>
-      <c r="I166" t="str">
+        <v>10</v>
+      </c>
+      <c r="I166">
+        <v>8</v>
+      </c>
+      <c r="J166" t="str">
         <v>1000051002861</v>
       </c>
     </row>
@@ -5233,12 +5731,15 @@
         <v>86000</v>
       </c>
       <c r="G167">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>8</v>
-      </c>
-      <c r="I167" t="str">
+        <v>10</v>
+      </c>
+      <c r="I167">
+        <v>8</v>
+      </c>
+      <c r="J167" t="str">
         <v>1000023001359</v>
       </c>
     </row>
@@ -5262,12 +5763,15 @@
         <v>86000</v>
       </c>
       <c r="G168">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>8</v>
-      </c>
-      <c r="I168" t="str">
+        <v>10</v>
+      </c>
+      <c r="I168">
+        <v>8</v>
+      </c>
+      <c r="J168" t="str">
         <v>1000051002878</v>
       </c>
     </row>
@@ -5291,12 +5795,15 @@
         <v>92000</v>
       </c>
       <c r="G169">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>8</v>
-      </c>
-      <c r="I169" t="str">
+        <v>10</v>
+      </c>
+      <c r="I169">
+        <v>8</v>
+      </c>
+      <c r="J169" t="str">
         <v>1000023001366</v>
       </c>
     </row>
@@ -5320,12 +5827,15 @@
         <v>92000</v>
       </c>
       <c r="G170">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>8</v>
-      </c>
-      <c r="I170" t="str">
+        <v>10</v>
+      </c>
+      <c r="I170">
+        <v>8</v>
+      </c>
+      <c r="J170" t="str">
         <v>1000051002885</v>
       </c>
     </row>
@@ -5349,12 +5859,15 @@
         <v>67000</v>
       </c>
       <c r="G171">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>8</v>
-      </c>
-      <c r="I171" t="str">
+        <v>10</v>
+      </c>
+      <c r="I171">
+        <v>8</v>
+      </c>
+      <c r="J171" t="str">
         <v>1000023001311</v>
       </c>
     </row>
@@ -5378,12 +5891,15 @@
         <v>67000</v>
       </c>
       <c r="G172">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>8</v>
-      </c>
-      <c r="I172" t="str">
+        <v>10</v>
+      </c>
+      <c r="I172">
+        <v>8</v>
+      </c>
+      <c r="J172" t="str">
         <v>1000051002830</v>
       </c>
     </row>
@@ -5407,12 +5923,15 @@
         <v>97000</v>
       </c>
       <c r="G173">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>8</v>
-      </c>
-      <c r="I173" t="str">
+        <v>10</v>
+      </c>
+      <c r="I173">
+        <v>8</v>
+      </c>
+      <c r="J173" t="str">
         <v>1000023001373</v>
       </c>
     </row>
@@ -5436,12 +5955,15 @@
         <v>97000</v>
       </c>
       <c r="G174">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H174">
-        <v>8</v>
-      </c>
-      <c r="I174" t="str">
+        <v>10</v>
+      </c>
+      <c r="I174">
+        <v>8</v>
+      </c>
+      <c r="J174" t="str">
         <v>1000051002892</v>
       </c>
     </row>
@@ -5465,12 +5987,15 @@
         <v>45000</v>
       </c>
       <c r="G175">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>8</v>
-      </c>
-      <c r="I175" t="str">
+        <v>10</v>
+      </c>
+      <c r="I175">
+        <v>8</v>
+      </c>
+      <c r="J175" t="str">
         <v>1000009000420</v>
       </c>
     </row>
@@ -5494,12 +6019,15 @@
         <v>45000</v>
       </c>
       <c r="G176">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>8</v>
-      </c>
-      <c r="I176" t="str">
+        <v>10</v>
+      </c>
+      <c r="I176">
+        <v>8</v>
+      </c>
+      <c r="J176" t="str">
         <v>1000033001943</v>
       </c>
     </row>
@@ -5523,12 +6051,15 @@
         <v>47000</v>
       </c>
       <c r="G177">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>8</v>
-      </c>
-      <c r="I177" t="str">
+        <v>10</v>
+      </c>
+      <c r="I177">
+        <v>8</v>
+      </c>
+      <c r="J177" t="str">
         <v>1000009000437</v>
       </c>
     </row>
@@ -5552,12 +6083,15 @@
         <v>47000</v>
       </c>
       <c r="G178">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>8</v>
-      </c>
-      <c r="I178" t="str">
+        <v>10</v>
+      </c>
+      <c r="I178">
+        <v>8</v>
+      </c>
+      <c r="J178" t="str">
         <v>1000033001950</v>
       </c>
     </row>
@@ -5581,12 +6115,15 @@
         <v>51000</v>
       </c>
       <c r="G179">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H179">
-        <v>8</v>
-      </c>
-      <c r="I179" t="str">
+        <v>10</v>
+      </c>
+      <c r="I179">
+        <v>8</v>
+      </c>
+      <c r="J179" t="str">
         <v>1000009000444</v>
       </c>
     </row>
@@ -5610,12 +6147,15 @@
         <v>51000</v>
       </c>
       <c r="G180">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H180">
-        <v>8</v>
-      </c>
-      <c r="I180" t="str">
+        <v>10</v>
+      </c>
+      <c r="I180">
+        <v>8</v>
+      </c>
+      <c r="J180" t="str">
         <v>1000033001967</v>
       </c>
     </row>
@@ -5639,12 +6179,15 @@
         <v>53000</v>
       </c>
       <c r="G181">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H181">
-        <v>8</v>
-      </c>
-      <c r="I181" t="str">
+        <v>10</v>
+      </c>
+      <c r="I181">
+        <v>8</v>
+      </c>
+      <c r="J181" t="str">
         <v>1000009000451</v>
       </c>
     </row>
@@ -5668,12 +6211,15 @@
         <v>53000</v>
       </c>
       <c r="G182">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H182">
-        <v>8</v>
-      </c>
-      <c r="I182" t="str">
+        <v>10</v>
+      </c>
+      <c r="I182">
+        <v>8</v>
+      </c>
+      <c r="J182" t="str">
         <v>1000033001974</v>
       </c>
     </row>
@@ -5697,12 +6243,15 @@
         <v>54000</v>
       </c>
       <c r="G183">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H183">
-        <v>8</v>
-      </c>
-      <c r="I183" t="str">
+        <v>10</v>
+      </c>
+      <c r="I183">
+        <v>8</v>
+      </c>
+      <c r="J183" t="str">
         <v>1000009000468</v>
       </c>
     </row>
@@ -5726,12 +6275,15 @@
         <v>54000</v>
       </c>
       <c r="G184">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>8</v>
-      </c>
-      <c r="I184" t="str">
+        <v>10</v>
+      </c>
+      <c r="I184">
+        <v>8</v>
+      </c>
+      <c r="J184" t="str">
         <v>1000033001981</v>
       </c>
     </row>
@@ -5755,12 +6307,15 @@
         <v>45000</v>
       </c>
       <c r="G185">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>8</v>
-      </c>
-      <c r="I185" t="str">
+        <v>10</v>
+      </c>
+      <c r="I185">
+        <v>8</v>
+      </c>
+      <c r="J185" t="str">
         <v>1000009000406</v>
       </c>
     </row>
@@ -5784,12 +6339,15 @@
         <v>45000</v>
       </c>
       <c r="G186">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H186">
-        <v>8</v>
-      </c>
-      <c r="I186" t="str">
+        <v>10</v>
+      </c>
+      <c r="I186">
+        <v>8</v>
+      </c>
+      <c r="J186" t="str">
         <v>1000033001929</v>
       </c>
     </row>
@@ -5813,12 +6371,15 @@
         <v>56000</v>
       </c>
       <c r="G187">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>8</v>
-      </c>
-      <c r="I187" t="str">
+        <v>10</v>
+      </c>
+      <c r="I187">
+        <v>8</v>
+      </c>
+      <c r="J187" t="str">
         <v>1000009000475</v>
       </c>
     </row>
@@ -5842,12 +6403,15 @@
         <v>56000</v>
       </c>
       <c r="G188">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H188">
-        <v>8</v>
-      </c>
-      <c r="I188" t="str">
+        <v>10</v>
+      </c>
+      <c r="I188">
+        <v>8</v>
+      </c>
+      <c r="J188" t="str">
         <v>1000033001998</v>
       </c>
     </row>
@@ -5871,12 +6435,15 @@
         <v>45000</v>
       </c>
       <c r="G189">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H189">
-        <v>8</v>
-      </c>
-      <c r="I189" t="str">
+        <v>10</v>
+      </c>
+      <c r="I189">
+        <v>8</v>
+      </c>
+      <c r="J189" t="str">
         <v>1000009000413</v>
       </c>
     </row>
@@ -5900,12 +6467,15 @@
         <v>45000</v>
       </c>
       <c r="G190">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H190">
-        <v>8</v>
-      </c>
-      <c r="I190" t="str">
+        <v>10</v>
+      </c>
+      <c r="I190">
+        <v>8</v>
+      </c>
+      <c r="J190" t="str">
         <v>1000033001936</v>
       </c>
     </row>
@@ -5929,12 +6499,15 @@
         <v>103000</v>
       </c>
       <c r="G191">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H191">
-        <v>8</v>
-      </c>
-      <c r="I191" t="str">
+        <v>10</v>
+      </c>
+      <c r="I191">
+        <v>8</v>
+      </c>
+      <c r="J191" t="str">
         <v>1000014000750</v>
       </c>
     </row>
@@ -5958,12 +6531,15 @@
         <v>100000</v>
       </c>
       <c r="G192">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>8</v>
-      </c>
-      <c r="I192" t="str">
+        <v>10</v>
+      </c>
+      <c r="I192">
+        <v>8</v>
+      </c>
+      <c r="J192" t="str">
         <v>1000027001638</v>
       </c>
     </row>
@@ -5987,12 +6563,15 @@
         <v>101000</v>
       </c>
       <c r="G193">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H193">
-        <v>8</v>
-      </c>
-      <c r="I193" t="str">
+        <v>10</v>
+      </c>
+      <c r="I193">
+        <v>8</v>
+      </c>
+      <c r="J193" t="str">
         <v>1000037002250</v>
       </c>
     </row>
@@ -6016,12 +6595,15 @@
         <v>110000</v>
       </c>
       <c r="G194">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H194">
-        <v>8</v>
-      </c>
-      <c r="I194" t="str">
+        <v>10</v>
+      </c>
+      <c r="I194">
+        <v>8</v>
+      </c>
+      <c r="J194" t="str">
         <v>1000014000767</v>
       </c>
     </row>
@@ -6045,12 +6627,15 @@
         <v>112000</v>
       </c>
       <c r="G195">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H195">
-        <v>8</v>
-      </c>
-      <c r="I195" t="str">
+        <v>10</v>
+      </c>
+      <c r="I195">
+        <v>8</v>
+      </c>
+      <c r="J195" t="str">
         <v>1000027001645</v>
       </c>
     </row>
@@ -6074,12 +6659,15 @@
         <v>108000</v>
       </c>
       <c r="G196">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H196">
-        <v>8</v>
-      </c>
-      <c r="I196" t="str">
+        <v>10</v>
+      </c>
+      <c r="I196">
+        <v>8</v>
+      </c>
+      <c r="J196" t="str">
         <v>1000037002267</v>
       </c>
     </row>
@@ -6103,12 +6691,15 @@
         <v>98000</v>
       </c>
       <c r="G197">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H197">
-        <v>8</v>
-      </c>
-      <c r="I197" t="str">
+        <v>10</v>
+      </c>
+      <c r="I197">
+        <v>8</v>
+      </c>
+      <c r="J197" t="str">
         <v>1000014000743</v>
       </c>
     </row>
@@ -6132,12 +6723,15 @@
         <v>105000</v>
       </c>
       <c r="G198">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H198">
-        <v>8</v>
-      </c>
-      <c r="I198" t="str">
+        <v>10</v>
+      </c>
+      <c r="I198">
+        <v>8</v>
+      </c>
+      <c r="J198" t="str">
         <v>1000027001621</v>
       </c>
     </row>
@@ -6161,12 +6755,15 @@
         <v>96000</v>
       </c>
       <c r="G199">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>8</v>
-      </c>
-      <c r="I199" t="str">
+        <v>10</v>
+      </c>
+      <c r="I199">
+        <v>8</v>
+      </c>
+      <c r="J199" t="str">
         <v>1000037002243</v>
       </c>
     </row>
@@ -6190,12 +6787,15 @@
         <v>137000</v>
       </c>
       <c r="G200">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>8</v>
-      </c>
-      <c r="I200" t="str">
+        <v>10</v>
+      </c>
+      <c r="I200">
+        <v>8</v>
+      </c>
+      <c r="J200" t="str">
         <v>1000014000798</v>
       </c>
     </row>
@@ -6219,12 +6819,15 @@
         <v>139000</v>
       </c>
       <c r="G201">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H201">
-        <v>8</v>
-      </c>
-      <c r="I201" t="str">
+        <v>10</v>
+      </c>
+      <c r="I201">
+        <v>8</v>
+      </c>
+      <c r="J201" t="str">
         <v>1000027001676</v>
       </c>
     </row>
@@ -6248,12 +6851,15 @@
         <v>133000</v>
       </c>
       <c r="G202">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H202">
-        <v>8</v>
-      </c>
-      <c r="I202" t="str">
+        <v>10</v>
+      </c>
+      <c r="I202">
+        <v>8</v>
+      </c>
+      <c r="J202" t="str">
         <v>1000037002298</v>
       </c>
     </row>
@@ -6277,12 +6883,15 @@
         <v>123000</v>
       </c>
       <c r="G203">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H203">
-        <v>8</v>
-      </c>
-      <c r="I203" t="str">
+        <v>10</v>
+      </c>
+      <c r="I203">
+        <v>8</v>
+      </c>
+      <c r="J203" t="str">
         <v>1000014000781</v>
       </c>
     </row>
@@ -6306,12 +6915,15 @@
         <v>130000</v>
       </c>
       <c r="G204">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H204">
-        <v>8</v>
-      </c>
-      <c r="I204" t="str">
+        <v>10</v>
+      </c>
+      <c r="I204">
+        <v>8</v>
+      </c>
+      <c r="J204" t="str">
         <v>1000027001669</v>
       </c>
     </row>
@@ -6335,12 +6947,15 @@
         <v>120000</v>
       </c>
       <c r="G205">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H205">
-        <v>8</v>
-      </c>
-      <c r="I205" t="str">
+        <v>10</v>
+      </c>
+      <c r="I205">
+        <v>8</v>
+      </c>
+      <c r="J205" t="str">
         <v>1000037002281</v>
       </c>
     </row>
@@ -6364,12 +6979,15 @@
         <v>142000</v>
       </c>
       <c r="G206">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>8</v>
-      </c>
-      <c r="I206" t="str">
+        <v>10</v>
+      </c>
+      <c r="I206">
+        <v>8</v>
+      </c>
+      <c r="J206" t="str">
         <v>1000014000804</v>
       </c>
     </row>
@@ -6393,12 +7011,15 @@
         <v>145000</v>
       </c>
       <c r="G207">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H207">
-        <v>8</v>
-      </c>
-      <c r="I207" t="str">
+        <v>10</v>
+      </c>
+      <c r="I207">
+        <v>8</v>
+      </c>
+      <c r="J207" t="str">
         <v>1000027001683</v>
       </c>
     </row>
@@ -6422,12 +7043,15 @@
         <v>140000</v>
       </c>
       <c r="G208">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H208">
-        <v>8</v>
-      </c>
-      <c r="I208" t="str">
+        <v>10</v>
+      </c>
+      <c r="I208">
+        <v>8</v>
+      </c>
+      <c r="J208" t="str">
         <v>1000037002304</v>
       </c>
     </row>
@@ -6451,12 +7075,15 @@
         <v>116000</v>
       </c>
       <c r="G209">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>8</v>
-      </c>
-      <c r="I209" t="str">
+        <v>10</v>
+      </c>
+      <c r="I209">
+        <v>8</v>
+      </c>
+      <c r="J209" t="str">
         <v>1000014000774</v>
       </c>
     </row>
@@ -6480,12 +7107,15 @@
         <v>123000</v>
       </c>
       <c r="G210">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H210">
-        <v>8</v>
-      </c>
-      <c r="I210" t="str">
+        <v>10</v>
+      </c>
+      <c r="I210">
+        <v>8</v>
+      </c>
+      <c r="J210" t="str">
         <v>1000027001652</v>
       </c>
     </row>
@@ -6509,12 +7139,15 @@
         <v>115000</v>
       </c>
       <c r="G211">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>8</v>
-      </c>
-      <c r="I211" t="str">
+        <v>10</v>
+      </c>
+      <c r="I211">
+        <v>8</v>
+      </c>
+      <c r="J211" t="str">
         <v>1000037002274</v>
       </c>
     </row>
@@ -6538,12 +7171,15 @@
         <v>150000</v>
       </c>
       <c r="G212">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H212">
-        <v>8</v>
-      </c>
-      <c r="I212" t="str">
+        <v>10</v>
+      </c>
+      <c r="I212">
+        <v>8</v>
+      </c>
+      <c r="J212" t="str">
         <v>1000014000811</v>
       </c>
     </row>
@@ -6567,12 +7203,15 @@
         <v>153000</v>
       </c>
       <c r="G213">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>8</v>
-      </c>
-      <c r="I213" t="str">
+        <v>10</v>
+      </c>
+      <c r="I213">
+        <v>8</v>
+      </c>
+      <c r="J213" t="str">
         <v>1000027001690</v>
       </c>
     </row>
@@ -6596,12 +7235,15 @@
         <v>146000</v>
       </c>
       <c r="G214">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H214">
-        <v>8</v>
-      </c>
-      <c r="I214" t="str">
+        <v>10</v>
+      </c>
+      <c r="I214">
+        <v>8</v>
+      </c>
+      <c r="J214" t="str">
         <v>1000037002311</v>
       </c>
     </row>
@@ -6625,12 +7267,15 @@
         <v>48000</v>
       </c>
       <c r="G215">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>8</v>
-      </c>
-      <c r="I215" t="str">
+        <v>10</v>
+      </c>
+      <c r="I215">
+        <v>8</v>
+      </c>
+      <c r="J215" t="str">
         <v>1000011000517</v>
       </c>
     </row>
@@ -6654,12 +7299,15 @@
         <v>48000</v>
       </c>
       <c r="G216">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>8</v>
-      </c>
-      <c r="I216" t="str">
+        <v>10</v>
+      </c>
+      <c r="I216">
+        <v>8</v>
+      </c>
+      <c r="J216" t="str">
         <v>1000024001396</v>
       </c>
     </row>
@@ -6683,12 +7331,15 @@
         <v>44000</v>
       </c>
       <c r="G217">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H217">
-        <v>8</v>
-      </c>
-      <c r="I217" t="str">
+        <v>10</v>
+      </c>
+      <c r="I217">
+        <v>8</v>
+      </c>
+      <c r="J217" t="str">
         <v>1000034002017</v>
       </c>
     </row>
@@ -6712,12 +7363,15 @@
         <v>50000</v>
       </c>
       <c r="G218">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>8</v>
-      </c>
-      <c r="I218" t="str">
+        <v>10</v>
+      </c>
+      <c r="I218">
+        <v>8</v>
+      </c>
+      <c r="J218" t="str">
         <v>1000011000524</v>
       </c>
     </row>
@@ -6741,12 +7395,15 @@
         <v>50000</v>
       </c>
       <c r="G219">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>8</v>
-      </c>
-      <c r="I219" t="str">
+        <v>10</v>
+      </c>
+      <c r="I219">
+        <v>8</v>
+      </c>
+      <c r="J219" t="str">
         <v>1000024001402</v>
       </c>
     </row>
@@ -6770,12 +7427,15 @@
         <v>45000</v>
       </c>
       <c r="G220">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H220">
-        <v>8</v>
-      </c>
-      <c r="I220" t="str">
+        <v>10</v>
+      </c>
+      <c r="I220">
+        <v>8</v>
+      </c>
+      <c r="J220" t="str">
         <v>1000034002024</v>
       </c>
     </row>
@@ -6799,12 +7459,15 @@
         <v>46000</v>
       </c>
       <c r="G221">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>8</v>
-      </c>
-      <c r="I221" t="str">
+        <v>10</v>
+      </c>
+      <c r="I221">
+        <v>8</v>
+      </c>
+      <c r="J221" t="str">
         <v>1000011000500</v>
       </c>
     </row>
@@ -6828,12 +7491,15 @@
         <v>46000</v>
       </c>
       <c r="G222">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H222">
-        <v>8</v>
-      </c>
-      <c r="I222" t="str">
+        <v>10</v>
+      </c>
+      <c r="I222">
+        <v>8</v>
+      </c>
+      <c r="J222" t="str">
         <v>1000024001389</v>
       </c>
     </row>
@@ -6857,12 +7523,15 @@
         <v>42000</v>
       </c>
       <c r="G223">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>8</v>
-      </c>
-      <c r="I223" t="str">
+        <v>10</v>
+      </c>
+      <c r="I223">
+        <v>8</v>
+      </c>
+      <c r="J223" t="str">
         <v>1000034002000</v>
       </c>
     </row>
@@ -6886,12 +7555,15 @@
         <v>60000</v>
       </c>
       <c r="G224">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H224">
-        <v>8</v>
-      </c>
-      <c r="I224" t="str">
+        <v>10</v>
+      </c>
+      <c r="I224">
+        <v>8</v>
+      </c>
+      <c r="J224" t="str">
         <v>1000011000555</v>
       </c>
     </row>
@@ -6915,12 +7587,15 @@
         <v>60000</v>
       </c>
       <c r="G225">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H225">
-        <v>8</v>
-      </c>
-      <c r="I225" t="str">
+        <v>10</v>
+      </c>
+      <c r="I225">
+        <v>8</v>
+      </c>
+      <c r="J225" t="str">
         <v>1000024001433</v>
       </c>
     </row>
@@ -6944,12 +7619,15 @@
         <v>55000</v>
       </c>
       <c r="G226">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>8</v>
-      </c>
-      <c r="I226" t="str">
+        <v>10</v>
+      </c>
+      <c r="I226">
+        <v>8</v>
+      </c>
+      <c r="J226" t="str">
         <v>1000034002055</v>
       </c>
     </row>
@@ -6973,12 +7651,15 @@
         <v>57000</v>
       </c>
       <c r="G227">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>8</v>
-      </c>
-      <c r="I227" t="str">
+        <v>10</v>
+      </c>
+      <c r="I227">
+        <v>8</v>
+      </c>
+      <c r="J227" t="str">
         <v>1000011000548</v>
       </c>
     </row>
@@ -7002,12 +7683,15 @@
         <v>57000</v>
       </c>
       <c r="G228">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>8</v>
-      </c>
-      <c r="I228" t="str">
+        <v>10</v>
+      </c>
+      <c r="I228">
+        <v>8</v>
+      </c>
+      <c r="J228" t="str">
         <v>1000024001426</v>
       </c>
     </row>
@@ -7031,12 +7715,15 @@
         <v>52000</v>
       </c>
       <c r="G229">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H229">
-        <v>8</v>
-      </c>
-      <c r="I229" t="str">
+        <v>10</v>
+      </c>
+      <c r="I229">
+        <v>8</v>
+      </c>
+      <c r="J229" t="str">
         <v>1000034002048</v>
       </c>
     </row>
@@ -7060,12 +7747,15 @@
         <v>62000</v>
       </c>
       <c r="G230">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H230">
-        <v>8</v>
-      </c>
-      <c r="I230" t="str">
+        <v>10</v>
+      </c>
+      <c r="I230">
+        <v>8</v>
+      </c>
+      <c r="J230" t="str">
         <v>1000011000562</v>
       </c>
     </row>
@@ -7089,12 +7779,15 @@
         <v>62000</v>
       </c>
       <c r="G231">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H231">
-        <v>8</v>
-      </c>
-      <c r="I231" t="str">
+        <v>10</v>
+      </c>
+      <c r="I231">
+        <v>8</v>
+      </c>
+      <c r="J231" t="str">
         <v>1000024001440</v>
       </c>
     </row>
@@ -7118,12 +7811,15 @@
         <v>58000</v>
       </c>
       <c r="G232">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H232">
-        <v>8</v>
-      </c>
-      <c r="I232" t="str">
+        <v>10</v>
+      </c>
+      <c r="I232">
+        <v>8</v>
+      </c>
+      <c r="J232" t="str">
         <v>1000034002062</v>
       </c>
     </row>
@@ -7147,12 +7843,15 @@
         <v>52000</v>
       </c>
       <c r="G233">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>8</v>
-      </c>
-      <c r="I233" t="str">
+        <v>10</v>
+      </c>
+      <c r="I233">
+        <v>8</v>
+      </c>
+      <c r="J233" t="str">
         <v>1000011000531</v>
       </c>
     </row>
@@ -7176,12 +7875,15 @@
         <v>52000</v>
       </c>
       <c r="G234">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H234">
-        <v>8</v>
-      </c>
-      <c r="I234" t="str">
+        <v>10</v>
+      </c>
+      <c r="I234">
+        <v>8</v>
+      </c>
+      <c r="J234" t="str">
         <v>1000024001419</v>
       </c>
     </row>
@@ -7205,12 +7907,15 @@
         <v>48000</v>
       </c>
       <c r="G235">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H235">
-        <v>8</v>
-      </c>
-      <c r="I235" t="str">
+        <v>10</v>
+      </c>
+      <c r="I235">
+        <v>8</v>
+      </c>
+      <c r="J235" t="str">
         <v>1000034002031</v>
       </c>
     </row>
@@ -7234,12 +7939,15 @@
         <v>65000</v>
       </c>
       <c r="G236">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H236">
-        <v>8</v>
-      </c>
-      <c r="I236" t="str">
+        <v>10</v>
+      </c>
+      <c r="I236">
+        <v>8</v>
+      </c>
+      <c r="J236" t="str">
         <v>1000011000579</v>
       </c>
     </row>
@@ -7263,12 +7971,15 @@
         <v>65000</v>
       </c>
       <c r="G237">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H237">
-        <v>8</v>
-      </c>
-      <c r="I237" t="str">
+        <v>10</v>
+      </c>
+      <c r="I237">
+        <v>8</v>
+      </c>
+      <c r="J237" t="str">
         <v>1000024001457</v>
       </c>
     </row>
@@ -7292,12 +8003,15 @@
         <v>62000</v>
       </c>
       <c r="G238">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H238">
-        <v>8</v>
-      </c>
-      <c r="I238" t="str">
+        <v>10</v>
+      </c>
+      <c r="I238">
+        <v>8</v>
+      </c>
+      <c r="J238" t="str">
         <v>1000034002079</v>
       </c>
     </row>
@@ -7321,12 +8035,15 @@
         <v>49000</v>
       </c>
       <c r="G239">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H239">
-        <v>8</v>
-      </c>
-      <c r="I239" t="str">
+        <v>10</v>
+      </c>
+      <c r="I239">
+        <v>8</v>
+      </c>
+      <c r="J239" t="str">
         <v>1000012000592</v>
       </c>
     </row>
@@ -7350,12 +8067,15 @@
         <v>56000</v>
       </c>
       <c r="G240">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H240">
-        <v>8</v>
-      </c>
-      <c r="I240" t="str">
+        <v>10</v>
+      </c>
+      <c r="I240">
+        <v>8</v>
+      </c>
+      <c r="J240" t="str">
         <v>1000025001470</v>
       </c>
     </row>
@@ -7379,12 +8099,15 @@
         <v>49000</v>
       </c>
       <c r="G241">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>8</v>
-      </c>
-      <c r="I241" t="str">
+        <v>10</v>
+      </c>
+      <c r="I241">
+        <v>8</v>
+      </c>
+      <c r="J241" t="str">
         <v>1000035002092</v>
       </c>
     </row>
@@ -7408,12 +8131,15 @@
         <v>52000</v>
       </c>
       <c r="G242">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H242">
-        <v>8</v>
-      </c>
-      <c r="I242" t="str">
+        <v>10</v>
+      </c>
+      <c r="I242">
+        <v>8</v>
+      </c>
+      <c r="J242" t="str">
         <v>1000012000608</v>
       </c>
     </row>
@@ -7437,12 +8163,15 @@
         <v>59000</v>
       </c>
       <c r="G243">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H243">
-        <v>8</v>
-      </c>
-      <c r="I243" t="str">
+        <v>10</v>
+      </c>
+      <c r="I243">
+        <v>8</v>
+      </c>
+      <c r="J243" t="str">
         <v>1000025001487</v>
       </c>
     </row>
@@ -7466,12 +8195,15 @@
         <v>52000</v>
       </c>
       <c r="G244">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H244">
-        <v>8</v>
-      </c>
-      <c r="I244" t="str">
+        <v>10</v>
+      </c>
+      <c r="I244">
+        <v>8</v>
+      </c>
+      <c r="J244" t="str">
         <v>1000035002108</v>
       </c>
     </row>
@@ -7495,12 +8227,15 @@
         <v>47000</v>
       </c>
       <c r="G245">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H245">
-        <v>8</v>
-      </c>
-      <c r="I245" t="str">
+        <v>10</v>
+      </c>
+      <c r="I245">
+        <v>8</v>
+      </c>
+      <c r="J245" t="str">
         <v>1000012000585</v>
       </c>
     </row>
@@ -7524,12 +8259,15 @@
         <v>54000</v>
       </c>
       <c r="G246">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>8</v>
-      </c>
-      <c r="I246" t="str">
+        <v>10</v>
+      </c>
+      <c r="I246">
+        <v>8</v>
+      </c>
+      <c r="J246" t="str">
         <v>1000025001463</v>
       </c>
     </row>
@@ -7553,12 +8291,15 @@
         <v>47000</v>
       </c>
       <c r="G247">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H247">
-        <v>8</v>
-      </c>
-      <c r="I247" t="str">
+        <v>10</v>
+      </c>
+      <c r="I247">
+        <v>8</v>
+      </c>
+      <c r="J247" t="str">
         <v>1000035002085</v>
       </c>
     </row>
@@ -7582,12 +8323,15 @@
         <v>62000</v>
       </c>
       <c r="G248">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H248">
-        <v>8</v>
-      </c>
-      <c r="I248" t="str">
+        <v>10</v>
+      </c>
+      <c r="I248">
+        <v>8</v>
+      </c>
+      <c r="J248" t="str">
         <v>1000012000639</v>
       </c>
     </row>
@@ -7611,12 +8355,15 @@
         <v>70000</v>
       </c>
       <c r="G249">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H249">
-        <v>8</v>
-      </c>
-      <c r="I249" t="str">
+        <v>10</v>
+      </c>
+      <c r="I249">
+        <v>8</v>
+      </c>
+      <c r="J249" t="str">
         <v>1000025001517</v>
       </c>
     </row>
@@ -7640,12 +8387,15 @@
         <v>62000</v>
       </c>
       <c r="G250">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H250">
-        <v>8</v>
-      </c>
-      <c r="I250" t="str">
+        <v>10</v>
+      </c>
+      <c r="I250">
+        <v>8</v>
+      </c>
+      <c r="J250" t="str">
         <v>1000035002139</v>
       </c>
     </row>
@@ -7669,12 +8419,15 @@
         <v>60000</v>
       </c>
       <c r="G251">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H251">
-        <v>8</v>
-      </c>
-      <c r="I251" t="str">
+        <v>10</v>
+      </c>
+      <c r="I251">
+        <v>8</v>
+      </c>
+      <c r="J251" t="str">
         <v>1000012000622</v>
       </c>
     </row>
@@ -7698,12 +8451,15 @@
         <v>68000</v>
       </c>
       <c r="G252">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H252">
-        <v>8</v>
-      </c>
-      <c r="I252" t="str">
+        <v>10</v>
+      </c>
+      <c r="I252">
+        <v>8</v>
+      </c>
+      <c r="J252" t="str">
         <v>1000025001500</v>
       </c>
     </row>
@@ -7727,12 +8483,15 @@
         <v>60000</v>
       </c>
       <c r="G253">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>8</v>
-      </c>
-      <c r="I253" t="str">
+        <v>10</v>
+      </c>
+      <c r="I253">
+        <v>8</v>
+      </c>
+      <c r="J253" t="str">
         <v>1000035002122</v>
       </c>
     </row>
@@ -7756,12 +8515,15 @@
         <v>65000</v>
       </c>
       <c r="G254">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H254">
-        <v>8</v>
-      </c>
-      <c r="I254" t="str">
+        <v>10</v>
+      </c>
+      <c r="I254">
+        <v>8</v>
+      </c>
+      <c r="J254" t="str">
         <v>1000012000646</v>
       </c>
     </row>
@@ -7785,12 +8547,15 @@
         <v>75000</v>
       </c>
       <c r="G255">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>8</v>
-      </c>
-      <c r="I255" t="str">
+        <v>10</v>
+      </c>
+      <c r="I255">
+        <v>8</v>
+      </c>
+      <c r="J255" t="str">
         <v>1000025001524</v>
       </c>
     </row>
@@ -7814,12 +8579,15 @@
         <v>70000</v>
       </c>
       <c r="G256">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H256">
-        <v>8</v>
-      </c>
-      <c r="I256" t="str">
+        <v>10</v>
+      </c>
+      <c r="I256">
+        <v>8</v>
+      </c>
+      <c r="J256" t="str">
         <v>1000035002146</v>
       </c>
     </row>
@@ -7843,12 +8611,15 @@
         <v>58000</v>
       </c>
       <c r="G257">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H257">
-        <v>8</v>
-      </c>
-      <c r="I257" t="str">
+        <v>10</v>
+      </c>
+      <c r="I257">
+        <v>8</v>
+      </c>
+      <c r="J257" t="str">
         <v>1000012000615</v>
       </c>
     </row>
@@ -7872,12 +8643,15 @@
         <v>64000</v>
       </c>
       <c r="G258">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H258">
-        <v>8</v>
-      </c>
-      <c r="I258" t="str">
+        <v>10</v>
+      </c>
+      <c r="I258">
+        <v>8</v>
+      </c>
+      <c r="J258" t="str">
         <v>1000025001494</v>
       </c>
     </row>
@@ -7901,12 +8675,15 @@
         <v>58000</v>
       </c>
       <c r="G259">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H259">
-        <v>8</v>
-      </c>
-      <c r="I259" t="str">
+        <v>10</v>
+      </c>
+      <c r="I259">
+        <v>8</v>
+      </c>
+      <c r="J259" t="str">
         <v>1000035002115</v>
       </c>
     </row>
@@ -7930,12 +8707,15 @@
         <v>73000</v>
       </c>
       <c r="G260">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H260">
-        <v>8</v>
-      </c>
-      <c r="I260" t="str">
+        <v>10</v>
+      </c>
+      <c r="I260">
+        <v>8</v>
+      </c>
+      <c r="J260" t="str">
         <v>1000012000653</v>
       </c>
     </row>
@@ -7959,12 +8739,15 @@
         <v>80000</v>
       </c>
       <c r="G261">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H261">
-        <v>8</v>
-      </c>
-      <c r="I261" t="str">
+        <v>10</v>
+      </c>
+      <c r="I261">
+        <v>8</v>
+      </c>
+      <c r="J261" t="str">
         <v>1000025001531</v>
       </c>
     </row>
@@ -7988,12 +8771,15 @@
         <v>73000</v>
       </c>
       <c r="G262">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H262">
-        <v>8</v>
-      </c>
-      <c r="I262" t="str">
+        <v>10</v>
+      </c>
+      <c r="I262">
+        <v>8</v>
+      </c>
+      <c r="J262" t="str">
         <v>1000035002153</v>
       </c>
     </row>
@@ -8017,12 +8803,15 @@
         <v>25000</v>
       </c>
       <c r="G263">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H263">
-        <v>8</v>
-      </c>
-      <c r="I263" t="str">
+        <v>10</v>
+      </c>
+      <c r="I263">
+        <v>8</v>
+      </c>
+      <c r="J263" t="str">
         <v>1000013000676</v>
       </c>
     </row>
@@ -8046,12 +8835,15 @@
         <v>25000</v>
       </c>
       <c r="G264">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H264">
-        <v>8</v>
-      </c>
-      <c r="I264" t="str">
+        <v>10</v>
+      </c>
+      <c r="I264">
+        <v>8</v>
+      </c>
+      <c r="J264" t="str">
         <v>1000026001554</v>
       </c>
     </row>
@@ -8075,12 +8867,15 @@
         <v>25000</v>
       </c>
       <c r="G265">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>8</v>
-      </c>
-      <c r="I265" t="str">
+        <v>10</v>
+      </c>
+      <c r="I265">
+        <v>8</v>
+      </c>
+      <c r="J265" t="str">
         <v>1000036002176</v>
       </c>
     </row>
@@ -8104,12 +8899,15 @@
         <v>28000</v>
       </c>
       <c r="G266">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H266">
-        <v>8</v>
-      </c>
-      <c r="I266" t="str">
+        <v>10</v>
+      </c>
+      <c r="I266">
+        <v>8</v>
+      </c>
+      <c r="J266" t="str">
         <v>1000013000683</v>
       </c>
     </row>
@@ -8133,12 +8931,15 @@
         <v>28000</v>
       </c>
       <c r="G267">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H267">
-        <v>8</v>
-      </c>
-      <c r="I267" t="str">
+        <v>10</v>
+      </c>
+      <c r="I267">
+        <v>8</v>
+      </c>
+      <c r="J267" t="str">
         <v>1000026001561</v>
       </c>
     </row>
@@ -8162,12 +8963,15 @@
         <v>28000</v>
       </c>
       <c r="G268">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>8</v>
-      </c>
-      <c r="I268" t="str">
+        <v>10</v>
+      </c>
+      <c r="I268">
+        <v>8</v>
+      </c>
+      <c r="J268" t="str">
         <v>1000036002183</v>
       </c>
     </row>
@@ -8191,12 +8995,15 @@
         <v>25000</v>
       </c>
       <c r="G269">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H269">
-        <v>8</v>
-      </c>
-      <c r="I269" t="str">
+        <v>10</v>
+      </c>
+      <c r="I269">
+        <v>8</v>
+      </c>
+      <c r="J269" t="str">
         <v>1000013000669</v>
       </c>
     </row>
@@ -8220,12 +9027,15 @@
         <v>25000</v>
       </c>
       <c r="G270">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H270">
-        <v>8</v>
-      </c>
-      <c r="I270" t="str">
+        <v>10</v>
+      </c>
+      <c r="I270">
+        <v>8</v>
+      </c>
+      <c r="J270" t="str">
         <v>1000026001547</v>
       </c>
     </row>
@@ -8249,12 +9059,15 @@
         <v>25000</v>
       </c>
       <c r="G271">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H271">
-        <v>8</v>
-      </c>
-      <c r="I271" t="str">
+        <v>10</v>
+      </c>
+      <c r="I271">
+        <v>8</v>
+      </c>
+      <c r="J271" t="str">
         <v>1000036002169</v>
       </c>
     </row>
@@ -8278,12 +9091,15 @@
         <v>37000</v>
       </c>
       <c r="G272">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H272">
-        <v>8</v>
-      </c>
-      <c r="I272" t="str">
+        <v>10</v>
+      </c>
+      <c r="I272">
+        <v>8</v>
+      </c>
+      <c r="J272" t="str">
         <v>1000013000713</v>
       </c>
     </row>
@@ -8307,12 +9123,15 @@
         <v>37000</v>
       </c>
       <c r="G273">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H273">
-        <v>8</v>
-      </c>
-      <c r="I273" t="str">
+        <v>10</v>
+      </c>
+      <c r="I273">
+        <v>8</v>
+      </c>
+      <c r="J273" t="str">
         <v>1000026001592</v>
       </c>
     </row>
@@ -8336,12 +9155,15 @@
         <v>37000</v>
       </c>
       <c r="G274">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H274">
-        <v>8</v>
-      </c>
-      <c r="I274" t="str">
+        <v>10</v>
+      </c>
+      <c r="I274">
+        <v>8</v>
+      </c>
+      <c r="J274" t="str">
         <v>1000036002213</v>
       </c>
     </row>
@@ -8365,12 +9187,15 @@
         <v>35000</v>
       </c>
       <c r="G275">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H275">
-        <v>8</v>
-      </c>
-      <c r="I275" t="str">
+        <v>10</v>
+      </c>
+      <c r="I275">
+        <v>8</v>
+      </c>
+      <c r="J275" t="str">
         <v>1000013000706</v>
       </c>
     </row>
@@ -8394,12 +9219,15 @@
         <v>35000</v>
       </c>
       <c r="G276">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H276">
-        <v>8</v>
-      </c>
-      <c r="I276" t="str">
+        <v>10</v>
+      </c>
+      <c r="I276">
+        <v>8</v>
+      </c>
+      <c r="J276" t="str">
         <v>1000026001585</v>
       </c>
     </row>
@@ -8423,12 +9251,15 @@
         <v>35000</v>
       </c>
       <c r="G277">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>8</v>
-      </c>
-      <c r="I277" t="str">
+        <v>10</v>
+      </c>
+      <c r="I277">
+        <v>8</v>
+      </c>
+      <c r="J277" t="str">
         <v>1000036002206</v>
       </c>
     </row>
@@ -8452,12 +9283,15 @@
         <v>42000</v>
       </c>
       <c r="G278">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H278">
-        <v>8</v>
-      </c>
-      <c r="I278" t="str">
+        <v>10</v>
+      </c>
+      <c r="I278">
+        <v>8</v>
+      </c>
+      <c r="J278" t="str">
         <v>1000013000720</v>
       </c>
     </row>
@@ -8481,12 +9315,15 @@
         <v>42000</v>
       </c>
       <c r="G279">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H279">
-        <v>8</v>
-      </c>
-      <c r="I279" t="str">
+        <v>10</v>
+      </c>
+      <c r="I279">
+        <v>8</v>
+      </c>
+      <c r="J279" t="str">
         <v>1000026001608</v>
       </c>
     </row>
@@ -8510,12 +9347,15 @@
         <v>42000</v>
       </c>
       <c r="G280">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H280">
-        <v>8</v>
-      </c>
-      <c r="I280" t="str">
+        <v>10</v>
+      </c>
+      <c r="I280">
+        <v>8</v>
+      </c>
+      <c r="J280" t="str">
         <v>1000036002220</v>
       </c>
     </row>
@@ -8539,12 +9379,15 @@
         <v>32000</v>
       </c>
       <c r="G281">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H281">
-        <v>8</v>
-      </c>
-      <c r="I281" t="str">
+        <v>10</v>
+      </c>
+      <c r="I281">
+        <v>8</v>
+      </c>
+      <c r="J281" t="str">
         <v>1000013000690</v>
       </c>
     </row>
@@ -8568,12 +9411,15 @@
         <v>32000</v>
       </c>
       <c r="G282">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H282">
-        <v>8</v>
-      </c>
-      <c r="I282" t="str">
+        <v>10</v>
+      </c>
+      <c r="I282">
+        <v>8</v>
+      </c>
+      <c r="J282" t="str">
         <v>1000026001578</v>
       </c>
     </row>
@@ -8597,12 +9443,15 @@
         <v>32000</v>
       </c>
       <c r="G283">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>8</v>
-      </c>
-      <c r="I283" t="str">
+        <v>10</v>
+      </c>
+      <c r="I283">
+        <v>8</v>
+      </c>
+      <c r="J283" t="str">
         <v>1000036002190</v>
       </c>
     </row>
@@ -8626,12 +9475,15 @@
         <v>45000</v>
       </c>
       <c r="G284">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H284">
-        <v>8</v>
-      </c>
-      <c r="I284" t="str">
+        <v>10</v>
+      </c>
+      <c r="I284">
+        <v>8</v>
+      </c>
+      <c r="J284" t="str">
         <v>1000013000737</v>
       </c>
     </row>
@@ -8655,12 +9507,15 @@
         <v>45000</v>
       </c>
       <c r="G285">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H285">
-        <v>8</v>
-      </c>
-      <c r="I285" t="str">
+        <v>10</v>
+      </c>
+      <c r="I285">
+        <v>8</v>
+      </c>
+      <c r="J285" t="str">
         <v>1000026001615</v>
       </c>
     </row>
@@ -8684,18 +9539,21 @@
         <v>45000</v>
       </c>
       <c r="G286">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H286">
-        <v>8</v>
-      </c>
-      <c r="I286" t="str">
+        <v>10</v>
+      </c>
+      <c r="I286">
+        <v>8</v>
+      </c>
+      <c r="J286" t="str">
         <v>1000036002237</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I286"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J286"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/inventario.xlsx
+++ b/reportes/inventario.xlsx
@@ -6022,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="H176">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I176">
         <v>8</v>
@@ -6502,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="H191">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I191">
         <v>8</v>
@@ -8102,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="H241">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I241">
         <v>8</v>

--- a/reportes/inventario.xlsx
+++ b/reportes/inventario.xlsx
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="H161">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I161">
         <v>8</v>
